--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">

--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">

--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">

--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">

--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">

--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">

--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">

--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">

--- a/Books.xlsx
+++ b/Books.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2">
